--- a/design/server framework.xlsx
+++ b/design/server framework.xlsx
@@ -5,15 +5,15 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtao/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtao/Desktop/microdust/design/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{59FBD3A7-A06A-F245-B938-E5A7A74F2723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F220535-A382-5D44-A615-C0D2143CEADF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2780" yWindow="1500" windowWidth="28040" windowHeight="17440" xr2:uid="{5A3D3624-5D26-1441-BDAF-17D207357B60}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Server Framework" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>MicroServices</t>
   </si>
@@ -59,6 +59,15 @@
   </si>
   <si>
     <t>RabbitMq</t>
+  </si>
+  <si>
+    <t>Tools</t>
+  </si>
+  <si>
+    <t>MapEditorService</t>
+  </si>
+  <si>
+    <t>ConfigService</t>
   </si>
 </sst>
 </file>
@@ -410,18 +419,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B6A2892-C262-4344-9339-9687B04DD429}">
-  <dimension ref="B3:J13"/>
+  <dimension ref="B3:O13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="6" max="6" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:15" x14ac:dyDescent="0.2">
       <c r="F3" t="s">
         <v>0</v>
       </c>
+      <c r="N3" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>3</v>
       </c>
@@ -437,13 +449,19 @@
       <c r="J5" t="s">
         <v>5</v>
       </c>
+      <c r="M5" t="s">
+        <v>10</v>
+      </c>
+      <c r="O5" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:15" x14ac:dyDescent="0.2">
       <c r="H7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.2">
       <c r="D13" t="s">
         <v>7</v>
       </c>
